--- a/Checklist.xlsx
+++ b/Checklist.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\git\hemsida\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{654F17F0-0A82-4717-B0EE-B85DEFFFC763}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BECB16D-EA03-4DB9-ACC2-94A4EA0138DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="31515" yWindow="4725" windowWidth="22950" windowHeight="13605" xr2:uid="{13CE45C2-7BDF-4003-AB3C-FBEE998F4DF9}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
   <si>
     <t>Serenia</t>
   </si>
@@ -87,13 +87,22 @@
   </si>
   <si>
     <t>renderTopMenu</t>
+  </si>
+  <si>
+    <t>No hifi in Tech/EN</t>
+  </si>
+  <si>
+    <t>To Fix</t>
+  </si>
+  <si>
+    <t>N/A</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -104,6 +113,14 @@
     <font>
       <sz val="11"/>
       <color theme="6"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -135,10 +152,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -473,15 +498,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D50BD556-0EDA-4124-8531-768A29A5C21F}">
-  <dimension ref="A1:B16"/>
+  <dimension ref="A1:B22"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.7109375" customWidth="1"/>
-    <col min="2" max="2" width="18" customWidth="1"/>
+    <col min="1" max="1" width="16.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18" style="2" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B1" t="s">
+      <c r="B1" s="2" t="s">
         <v>15</v>
       </c>
     </row>
@@ -489,79 +514,102 @@
       <c r="A2" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="2"/>
+      <c r="B2" s="3"/>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="2"/>
+      <c r="B3" s="3"/>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>2</v>
       </c>
+      <c r="B4" s="3"/>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>3</v>
       </c>
+      <c r="B5" s="3"/>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>4</v>
       </c>
+      <c r="B6" s="3"/>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="1"/>
+      <c r="B7" s="4"/>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>6</v>
       </c>
+      <c r="B8" s="4"/>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>7</v>
       </c>
+      <c r="B9" s="4"/>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>8</v>
       </c>
+      <c r="B10" s="4"/>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>9</v>
       </c>
+      <c r="B11" s="4"/>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>10</v>
       </c>
+      <c r="B12" s="4"/>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>11</v>
       </c>
+      <c r="B13" s="4"/>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>12</v>
       </c>
+      <c r="B14" s="4"/>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>13</v>
       </c>
-      <c r="B15" s="1"/>
+      <c r="B15" s="4"/>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>14</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>16</v>
       </c>
     </row>
   </sheetData>
